--- a/produktjakt/korningar/2026-09-10/Leverantorsoffert-2026-09-10.xlsx
+++ b/produktjakt/korningar/2026-09-10/Leverantorsoffert-2026-09-10.xlsx
@@ -732,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU16"/>
+  <dimension ref="A1:AU12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="71" min="1" max="1"/>
@@ -767,7 +767,7 @@
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" s="71">
       <c r="A1" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP1" s="1" t="n"/>
       <c r="AQ1" s="1" t="n"/>
@@ -1027,17 +1027,17 @@
     </row>
     <row r="5" ht="24" customHeight="1" s="71">
       <c r="A5" s="10">
-        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/S81ca1b5c4bfb404c9a9478bb65b4aa7en.jpg")</f>
+        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/Sbf7d8a030fee4a34b489f30b34986ef6b.jpg")</f>
         <v/>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>Automotive Leveling Ramps RV Leveling Ramps Car Wheel Chocks Sturdy Th…</t>
+          <t>LEAORLD 12V 10W MPPT Solar Battery Charger Maintainer, Solar Panel Tri…</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>AliExpress: US $22.17. Vår räkning: landad ca 318 kr, tänkt butikspris 799 kr. Originaltitel: 2PCS Automotive Leveling Ramps RV Leveling Ramps Car Wheel Chocks Sturdy Three Step Tire Support for Trailers campers RV SUV</t>
+          <t>AliExpress: US $25.56. Vår räkning: landad ca 367 kr, tänkt butikspris 899 kr. Originaltitel: LEAORLD 12V 10W MPPT Solar Battery Charger Maintainer, Solar Panel Trickle Charging Kit For 12V Battery For Car Boat Marine RV</t>
         </is>
       </c>
       <c r="H5" s="13" t="n"/>
@@ -1052,7 +1052,7 @@
       <c r="M5" s="14" t="n"/>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.com/item/1005010788535191.html</t>
+          <t>https://www.aliexpress.com/item/1005011707131795.html</t>
         </is>
       </c>
       <c r="Q5" s="18" t="n"/>
@@ -1200,17 +1200,17 @@
     </row>
     <row r="9" ht="24" customHeight="1" s="71">
       <c r="A9" s="10">
-        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/Sbf7d8a030fee4a34b489f30b34986ef6b.jpg")</f>
+        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/S285a95bb17834cdc964b778e4ab9a080L.jpg")</f>
         <v/>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>LEAORLD 12V 10W MPPT Solar Battery Charger Maintainer, Solar Panel Tri…</t>
+          <t>Deer Hanger Pulley Lift System Rated 700 Lbs Gambrel for Skinning with…</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>AliExpress: US $25.56. Vår räkning: landad ca 367 kr, tänkt butikspris 899 kr. Originaltitel: LEAORLD 12V 10W MPPT Solar Battery Charger Maintainer, Solar Panel Trickle Charging Kit For 12V Battery For Car Boat Marine RV</t>
+          <t>AliExpress: US $16.89. Vår räkning: landad ca 242 kr, tänkt butikspris 599 kr. Originaltitel: Deer Hanger Pulley Lift System Rated 700 Lbs Gambrel for Skinning with Wear-Resistant Tangle-Free Rope Deer Hunting Accessories</t>
         </is>
       </c>
       <c r="H9" s="13" t="n"/>
@@ -1225,7 +1225,7 @@
       <c r="M9" s="14" t="n"/>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.com/item/1005011707131795.html</t>
+          <t>https://www.aliexpress.com/item/1005012116406743.html</t>
         </is>
       </c>
       <c r="Q9" s="18" t="n"/>
@@ -1371,179 +1371,10 @@
       <c r="AT12" s="35" t="n"/>
       <c r="AU12" s="35" t="n"/>
     </row>
-    <row r="13" ht="24" customHeight="1" s="71">
-      <c r="A13" s="10">
-        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/S285a95bb17834cdc964b778e4ab9a080L.jpg")</f>
-        <v/>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>Deer Hanger Pulley Lift System Rated 700 Lbs Gambrel for Skinning with…</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>AliExpress: US $16.89. Vår räkning: landad ca 242 kr, tänkt butikspris 599 kr. Originaltitel: Deer Hanger Pulley Lift System Rated 700 Lbs Gambrel for Skinning with Wear-Resistant Tangle-Free Rope Deer Hunting Accessories</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>SWEDEN</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="n"/>
-      <c r="K13" s="15" t="n"/>
-      <c r="L13" s="16" t="n"/>
-      <c r="M13" s="14" t="n"/>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>https://www.aliexpress.com/item/1005012116406743.html</t>
-        </is>
-      </c>
-      <c r="Q13" s="18" t="n"/>
-      <c r="R13" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="S13" s="15" t="n"/>
-      <c r="T13" s="15" t="n"/>
-      <c r="U13" s="16" t="n"/>
-      <c r="V13" s="48" t="n"/>
-      <c r="W13" s="48" t="n"/>
-      <c r="X13" s="21" t="n"/>
-      <c r="Y13" s="15" t="n"/>
-      <c r="Z13" s="15" t="n"/>
-      <c r="AA13" s="16" t="n"/>
-      <c r="AB13" s="48" t="n"/>
-      <c r="AC13" s="48" t="n"/>
-      <c r="AD13" s="22" t="n"/>
-      <c r="AE13" s="15" t="n"/>
-      <c r="AF13" s="15" t="n"/>
-      <c r="AG13" s="16" t="n"/>
-      <c r="AH13" s="48" t="n"/>
-      <c r="AI13" s="48" t="n"/>
-      <c r="AJ13" s="23" t="n"/>
-      <c r="AK13" s="15" t="n"/>
-      <c r="AL13" s="15" t="n"/>
-      <c r="AM13" s="16" t="n"/>
-      <c r="AN13" s="25" t="n"/>
-      <c r="AO13" s="48" t="n"/>
-      <c r="AP13" s="23" t="n"/>
-      <c r="AQ13" s="15" t="n"/>
-      <c r="AR13" s="15" t="n"/>
-      <c r="AS13" s="16" t="n"/>
-      <c r="AT13" s="25" t="n"/>
-      <c r="AU13" s="26" t="n"/>
-    </row>
-    <row r="14" ht="25.5" customHeight="1" s="71">
-      <c r="D14" s="18" t="n"/>
-      <c r="J14" s="15" t="n"/>
-      <c r="K14" s="15" t="n"/>
-      <c r="L14" s="16" t="n"/>
-      <c r="R14" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S14" s="15" t="n"/>
-      <c r="T14" s="15" t="n"/>
-      <c r="U14" s="16" t="n"/>
-      <c r="X14" s="21" t="n"/>
-      <c r="Y14" s="15" t="n"/>
-      <c r="Z14" s="15" t="n"/>
-      <c r="AA14" s="16" t="n"/>
-      <c r="AD14" s="22" t="n"/>
-      <c r="AE14" s="15" t="n"/>
-      <c r="AF14" s="15" t="n"/>
-      <c r="AG14" s="16" t="n"/>
-      <c r="AH14" s="48" t="n"/>
-      <c r="AI14" s="48" t="n"/>
-      <c r="AJ14" s="23" t="n"/>
-      <c r="AK14" s="15" t="n"/>
-      <c r="AL14" s="15" t="n"/>
-      <c r="AM14" s="16" t="n"/>
-      <c r="AP14" s="23" t="n"/>
-      <c r="AQ14" s="15" t="n"/>
-      <c r="AR14" s="15" t="n"/>
-      <c r="AS14" s="16" t="n"/>
-    </row>
-    <row r="15" s="71">
-      <c r="D15" s="18" t="n"/>
-      <c r="J15" s="15" t="n"/>
-      <c r="K15" s="15" t="n"/>
-      <c r="L15" s="16" t="n"/>
-      <c r="R15" s="19" t="n">
-        <v>300</v>
-      </c>
-      <c r="S15" s="15" t="n"/>
-      <c r="T15" s="15" t="n"/>
-      <c r="U15" s="16" t="n"/>
-      <c r="X15" s="21" t="n"/>
-      <c r="Y15" s="15" t="n"/>
-      <c r="Z15" s="15" t="n"/>
-      <c r="AA15" s="16" t="n"/>
-      <c r="AD15" s="22" t="n"/>
-      <c r="AE15" s="15" t="n"/>
-      <c r="AF15" s="15" t="n"/>
-      <c r="AG15" s="16" t="n"/>
-      <c r="AH15" s="48" t="n"/>
-      <c r="AI15" s="48" t="n"/>
-      <c r="AJ15" s="23" t="n"/>
-      <c r="AK15" s="15" t="n"/>
-      <c r="AL15" s="15" t="n"/>
-      <c r="AM15" s="16" t="n"/>
-      <c r="AP15" s="23" t="n"/>
-      <c r="AQ15" s="15" t="n"/>
-      <c r="AR15" s="15" t="n"/>
-      <c r="AS15" s="16" t="n"/>
-    </row>
-    <row r="16" ht="6.75" customHeight="1" s="71">
-      <c r="A16" s="27" t="n"/>
-      <c r="B16" s="27" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="27" t="n"/>
-      <c r="H16" s="35" t="n"/>
-      <c r="I16" s="35" t="n"/>
-      <c r="J16" s="36" t="n"/>
-      <c r="K16" s="36" t="n"/>
-      <c r="L16" s="36" t="n"/>
-      <c r="M16" s="35" t="n"/>
-      <c r="N16" s="30" t="n"/>
-      <c r="O16" s="30" t="n"/>
-      <c r="P16" s="30" t="n"/>
-      <c r="Q16" s="30" t="n"/>
-      <c r="R16" s="35" t="n"/>
-      <c r="S16" s="35" t="n"/>
-      <c r="T16" s="35" t="n"/>
-      <c r="U16" s="35" t="n"/>
-      <c r="V16" s="35" t="n"/>
-      <c r="W16" s="35" t="n"/>
-      <c r="X16" s="31" t="n"/>
-      <c r="Y16" s="35" t="n"/>
-      <c r="Z16" s="35" t="n"/>
-      <c r="AA16" s="36" t="n"/>
-      <c r="AB16" s="35" t="n"/>
-      <c r="AC16" s="35" t="n"/>
-      <c r="AD16" s="32" t="n"/>
-      <c r="AE16" s="35" t="n"/>
-      <c r="AF16" s="35" t="n"/>
-      <c r="AG16" s="36" t="n"/>
-      <c r="AH16" s="35" t="n"/>
-      <c r="AI16" s="35" t="n"/>
-      <c r="AJ16" s="34" t="n"/>
-      <c r="AK16" s="35" t="n"/>
-      <c r="AL16" s="35" t="n"/>
-      <c r="AM16" s="36" t="n"/>
-      <c r="AN16" s="35" t="n"/>
-      <c r="AO16" s="35" t="n"/>
-      <c r="AP16" s="34" t="n"/>
-      <c r="AQ16" s="35" t="n"/>
-      <c r="AR16" s="35" t="n"/>
-      <c r="AS16" s="36" t="n"/>
-      <c r="AT16" s="35" t="n"/>
-      <c r="AU16" s="35" t="n"/>
-    </row>
+    <row r="13" ht="22.5" customHeight="1" s="71"/>
+    <row r="14" ht="22.5" customHeight="1" s="71"/>
+    <row r="15" ht="22.5" customHeight="1" s="71"/>
+    <row r="16" ht="6.75" customHeight="1" s="71"/>
     <row r="17" ht="22.5" customHeight="1" s="71"/>
     <row r="18" ht="22.5" customHeight="1" s="71"/>
     <row r="19" ht="22.5" customHeight="1" s="71"/>
@@ -2529,32 +2360,26 @@
     <row r="999" ht="15.75" customHeight="1" s="71"/>
     <row r="1000" ht="15.75" customHeight="1" s="71"/>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="31">
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="E5:G7"/>
     <mergeCell ref="Q9:Q11"/>
     <mergeCell ref="L3:L4"/>
-    <mergeCell ref="E13:G15"/>
     <mergeCell ref="X3:AC3"/>
     <mergeCell ref="N5:P7"/>
-    <mergeCell ref="H13:H15"/>
     <mergeCell ref="E3:G4"/>
     <mergeCell ref="AJ3:AO3"/>
-    <mergeCell ref="I13:I15"/>
     <mergeCell ref="E9:G11"/>
     <mergeCell ref="R3:W3"/>
     <mergeCell ref="A1:AO1"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="I3:I4"/>
-    <mergeCell ref="Q13:Q15"/>
-    <mergeCell ref="N13:P15"/>
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="A5:C7"/>
     <mergeCell ref="N3:P4"/>
     <mergeCell ref="M9:M11"/>
     <mergeCell ref="M5:M7"/>
-    <mergeCell ref="A13:C15"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="N9:P11"/>
     <mergeCell ref="J3:J4"/>
@@ -2567,7 +2392,6 @@
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="A9:C11"/>
     <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="M13:M15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/produktjakt/korningar/2026-09-10/Leverantorsoffert-2026-09-10.xlsx
+++ b/produktjakt/korningar/2026-09-10/Leverantorsoffert-2026-09-10.xlsx
@@ -732,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AU24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="71" min="1" max="1"/>
@@ -767,7 +767,7 @@
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" s="71">
       <c r="A1" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AP1" s="1" t="n"/>
       <c r="AQ1" s="1" t="n"/>
@@ -1027,17 +1027,17 @@
     </row>
     <row r="5" ht="24" customHeight="1" s="71">
       <c r="A5" s="10">
-        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/Sbf7d8a030fee4a34b489f30b34986ef6b.jpg")</f>
+        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/S57c5c37f62304c378df2840912d4c4dbZ.png")</f>
         <v/>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>LEAORLD 12V 10W MPPT Solar Battery Charger Maintainer, Solar Panel Tri…</t>
+          <t>Caravan Front Protection Cover 200x160CM Black Weatherproof Towing Shi…</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>AliExpress: US $25.56. Vår räkning: landad ca 367 kr, tänkt butikspris 899 kr. Originaltitel: LEAORLD 12V 10W MPPT Solar Battery Charger Maintainer, Solar Panel Trickle Charging Kit For 12V Battery For Car Boat Marine RV</t>
+          <t>AliExpress: US $15.99. Vår räkning: landad ca 230 kr, tänkt butikspris 799 kr. Originaltitel: Caravan Front Protection Cover 200x160CM Black Weatherproof Towing Shield Bug Proof Keder Piping Hook Fastening</t>
         </is>
       </c>
       <c r="H5" s="13" t="n"/>
@@ -1052,7 +1052,7 @@
       <c r="M5" s="14" t="n"/>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.com/item/1005011707131795.html</t>
+          <t>https://www.aliexpress.com/item/1005012847791765.html</t>
         </is>
       </c>
       <c r="Q5" s="18" t="n"/>
@@ -1200,17 +1200,17 @@
     </row>
     <row r="9" ht="24" customHeight="1" s="71">
       <c r="A9" s="10">
-        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/S285a95bb17834cdc964b778e4ab9a080L.jpg")</f>
+        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/S2b98ac777d4a4ae5b0a681efb7e7081fT.jpg")</f>
         <v/>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Deer Hanger Pulley Lift System Rated 700 Lbs Gambrel for Skinning with…</t>
+          <t>Round Bathtub Cover Outdoor Anti-Uv Spa Hot Tub Dust Cover Foldable Su…</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>AliExpress: US $16.89. Vår räkning: landad ca 242 kr, tänkt butikspris 599 kr. Originaltitel: Deer Hanger Pulley Lift System Rated 700 Lbs Gambrel for Skinning with Wear-Resistant Tangle-Free Rope Deer Hunting Accessories</t>
+          <t>AliExpress: US $12.95. Vår räkning: landad ca 186 kr, tänkt butikspris 699 kr. Originaltitel: Round Bathtub Cover Outdoor Anti-Uv Spa Hot Tub Dust Cover Foldable Sunscreen Dustproof Waterproof Covers Swimming Pool Cover</t>
         </is>
       </c>
       <c r="H9" s="13" t="n"/>
@@ -1225,7 +1225,7 @@
       <c r="M9" s="14" t="n"/>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>https://www.aliexpress.com/item/1005012116406743.html</t>
+          <t>https://www.aliexpress.com/item/1005009353851718.html</t>
         </is>
       </c>
       <c r="Q9" s="18" t="n"/>
@@ -1371,18 +1371,525 @@
       <c r="AT12" s="35" t="n"/>
       <c r="AU12" s="35" t="n"/>
     </row>
-    <row r="13" ht="22.5" customHeight="1" s="71"/>
-    <row r="14" ht="22.5" customHeight="1" s="71"/>
-    <row r="15" ht="22.5" customHeight="1" s="71"/>
-    <row r="16" ht="6.75" customHeight="1" s="71"/>
-    <row r="17" ht="22.5" customHeight="1" s="71"/>
-    <row r="18" ht="22.5" customHeight="1" s="71"/>
-    <row r="19" ht="22.5" customHeight="1" s="71"/>
-    <row r="20" ht="6.75" customHeight="1" s="71"/>
-    <row r="21" ht="22.5" customHeight="1" s="71"/>
-    <row r="22" ht="22.5" customHeight="1" s="71"/>
-    <row r="23" ht="22.5" customHeight="1" s="71"/>
-    <row r="24" ht="6.75" customHeight="1" s="71"/>
+    <row r="13" ht="24" customHeight="1" s="71">
+      <c r="A13" s="10">
+        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/S46593c3e6999493c8eb24fb3f94888afz.jpg")</f>
+        <v/>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Log Rack Cover Outdoor Waterproof Wind/Snow Proof Firewood Covers Log …</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>AliExpress: US $24.79. Vår räkning: landad ca 356 kr, tänkt butikspris 899 kr. Originaltitel: Log Rack Cover Outdoor Waterproof Wind/Snow Proof Firewood Covers Log Storage Covering for Patio Garden Backyard Oxford Fabric</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>SWEDEN</t>
+        </is>
+      </c>
+      <c r="J13" s="15" t="n"/>
+      <c r="K13" s="15" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="14" t="n"/>
+      <c r="N13" s="17" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.com/item/1005011836511820.html</t>
+        </is>
+      </c>
+      <c r="Q13" s="18" t="n"/>
+      <c r="R13" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" s="15" t="n"/>
+      <c r="T13" s="15" t="n"/>
+      <c r="U13" s="16" t="n"/>
+      <c r="V13" s="48" t="n"/>
+      <c r="W13" s="48" t="n"/>
+      <c r="X13" s="21" t="n"/>
+      <c r="Y13" s="15" t="n"/>
+      <c r="Z13" s="15" t="n"/>
+      <c r="AA13" s="16" t="n"/>
+      <c r="AB13" s="48" t="n"/>
+      <c r="AC13" s="48" t="n"/>
+      <c r="AD13" s="22" t="n"/>
+      <c r="AE13" s="15" t="n"/>
+      <c r="AF13" s="15" t="n"/>
+      <c r="AG13" s="16" t="n"/>
+      <c r="AH13" s="48" t="n"/>
+      <c r="AI13" s="48" t="n"/>
+      <c r="AJ13" s="23" t="n"/>
+      <c r="AK13" s="15" t="n"/>
+      <c r="AL13" s="15" t="n"/>
+      <c r="AM13" s="16" t="n"/>
+      <c r="AN13" s="25" t="n"/>
+      <c r="AO13" s="48" t="n"/>
+      <c r="AP13" s="23" t="n"/>
+      <c r="AQ13" s="15" t="n"/>
+      <c r="AR13" s="15" t="n"/>
+      <c r="AS13" s="16" t="n"/>
+      <c r="AT13" s="25" t="n"/>
+      <c r="AU13" s="26" t="n"/>
+    </row>
+    <row r="14" ht="25.5" customHeight="1" s="71">
+      <c r="D14" s="18" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="R14" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="S14" s="15" t="n"/>
+      <c r="T14" s="15" t="n"/>
+      <c r="U14" s="16" t="n"/>
+      <c r="X14" s="21" t="n"/>
+      <c r="Y14" s="15" t="n"/>
+      <c r="Z14" s="15" t="n"/>
+      <c r="AA14" s="16" t="n"/>
+      <c r="AD14" s="22" t="n"/>
+      <c r="AE14" s="15" t="n"/>
+      <c r="AF14" s="15" t="n"/>
+      <c r="AG14" s="16" t="n"/>
+      <c r="AH14" s="48" t="n"/>
+      <c r="AI14" s="48" t="n"/>
+      <c r="AJ14" s="23" t="n"/>
+      <c r="AK14" s="15" t="n"/>
+      <c r="AL14" s="15" t="n"/>
+      <c r="AM14" s="16" t="n"/>
+      <c r="AP14" s="23" t="n"/>
+      <c r="AQ14" s="15" t="n"/>
+      <c r="AR14" s="15" t="n"/>
+      <c r="AS14" s="16" t="n"/>
+    </row>
+    <row r="15" s="71">
+      <c r="D15" s="18" t="n"/>
+      <c r="J15" s="15" t="n"/>
+      <c r="K15" s="15" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="R15" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="S15" s="15" t="n"/>
+      <c r="T15" s="15" t="n"/>
+      <c r="U15" s="16" t="n"/>
+      <c r="X15" s="21" t="n"/>
+      <c r="Y15" s="15" t="n"/>
+      <c r="Z15" s="15" t="n"/>
+      <c r="AA15" s="16" t="n"/>
+      <c r="AD15" s="22" t="n"/>
+      <c r="AE15" s="15" t="n"/>
+      <c r="AF15" s="15" t="n"/>
+      <c r="AG15" s="16" t="n"/>
+      <c r="AH15" s="48" t="n"/>
+      <c r="AI15" s="48" t="n"/>
+      <c r="AJ15" s="23" t="n"/>
+      <c r="AK15" s="15" t="n"/>
+      <c r="AL15" s="15" t="n"/>
+      <c r="AM15" s="16" t="n"/>
+      <c r="AP15" s="23" t="n"/>
+      <c r="AQ15" s="15" t="n"/>
+      <c r="AR15" s="15" t="n"/>
+      <c r="AS15" s="16" t="n"/>
+    </row>
+    <row r="16" ht="6.75" customHeight="1" s="71">
+      <c r="A16" s="27" t="n"/>
+      <c r="B16" s="27" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
+      <c r="H16" s="35" t="n"/>
+      <c r="I16" s="35" t="n"/>
+      <c r="J16" s="36" t="n"/>
+      <c r="K16" s="36" t="n"/>
+      <c r="L16" s="36" t="n"/>
+      <c r="M16" s="35" t="n"/>
+      <c r="N16" s="30" t="n"/>
+      <c r="O16" s="30" t="n"/>
+      <c r="P16" s="30" t="n"/>
+      <c r="Q16" s="30" t="n"/>
+      <c r="R16" s="35" t="n"/>
+      <c r="S16" s="35" t="n"/>
+      <c r="T16" s="35" t="n"/>
+      <c r="U16" s="35" t="n"/>
+      <c r="V16" s="35" t="n"/>
+      <c r="W16" s="35" t="n"/>
+      <c r="X16" s="31" t="n"/>
+      <c r="Y16" s="35" t="n"/>
+      <c r="Z16" s="35" t="n"/>
+      <c r="AA16" s="36" t="n"/>
+      <c r="AB16" s="35" t="n"/>
+      <c r="AC16" s="35" t="n"/>
+      <c r="AD16" s="32" t="n"/>
+      <c r="AE16" s="35" t="n"/>
+      <c r="AF16" s="35" t="n"/>
+      <c r="AG16" s="36" t="n"/>
+      <c r="AH16" s="35" t="n"/>
+      <c r="AI16" s="35" t="n"/>
+      <c r="AJ16" s="34" t="n"/>
+      <c r="AK16" s="35" t="n"/>
+      <c r="AL16" s="35" t="n"/>
+      <c r="AM16" s="36" t="n"/>
+      <c r="AN16" s="35" t="n"/>
+      <c r="AO16" s="35" t="n"/>
+      <c r="AP16" s="34" t="n"/>
+      <c r="AQ16" s="35" t="n"/>
+      <c r="AR16" s="35" t="n"/>
+      <c r="AS16" s="36" t="n"/>
+      <c r="AT16" s="35" t="n"/>
+      <c r="AU16" s="35" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1" s="71">
+      <c r="A17" s="10">
+        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/Sbf7d8a030fee4a34b489f30b34986ef6b.jpg")</f>
+        <v/>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>LEAORLD 12V 10W MPPT Solar Battery Charger Maintainer, Solar Panel Tri…</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>AliExpress: US $25.56. Vår räkning: landad ca 367 kr, tänkt butikspris 899 kr. Originaltitel: LEAORLD 12V 10W MPPT Solar Battery Charger Maintainer, Solar Panel Trickle Charging Kit For 12V Battery For Car Boat Marine RV</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>SWEDEN</t>
+        </is>
+      </c>
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="15" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="17" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.com/item/1005011707131795.html</t>
+        </is>
+      </c>
+      <c r="Q17" s="18" t="n"/>
+      <c r="R17" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="S17" s="15" t="n"/>
+      <c r="T17" s="15" t="n"/>
+      <c r="U17" s="16" t="n"/>
+      <c r="V17" s="48" t="n"/>
+      <c r="W17" s="48" t="n"/>
+      <c r="X17" s="21" t="n"/>
+      <c r="Y17" s="15" t="n"/>
+      <c r="Z17" s="15" t="n"/>
+      <c r="AA17" s="16" t="n"/>
+      <c r="AB17" s="48" t="n"/>
+      <c r="AC17" s="48" t="n"/>
+      <c r="AD17" s="22" t="n"/>
+      <c r="AE17" s="15" t="n"/>
+      <c r="AF17" s="15" t="n"/>
+      <c r="AG17" s="16" t="n"/>
+      <c r="AH17" s="48" t="n"/>
+      <c r="AI17" s="48" t="n"/>
+      <c r="AJ17" s="23" t="n"/>
+      <c r="AK17" s="15" t="n"/>
+      <c r="AL17" s="15" t="n"/>
+      <c r="AM17" s="16" t="n"/>
+      <c r="AN17" s="25" t="n"/>
+      <c r="AO17" s="48" t="n"/>
+      <c r="AP17" s="23" t="n"/>
+      <c r="AQ17" s="15" t="n"/>
+      <c r="AR17" s="15" t="n"/>
+      <c r="AS17" s="16" t="n"/>
+      <c r="AT17" s="25" t="n"/>
+      <c r="AU17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="25.5" customHeight="1" s="71">
+      <c r="D18" s="18" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="R18" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="S18" s="15" t="n"/>
+      <c r="T18" s="15" t="n"/>
+      <c r="U18" s="16" t="n"/>
+      <c r="X18" s="21" t="n"/>
+      <c r="Y18" s="15" t="n"/>
+      <c r="Z18" s="15" t="n"/>
+      <c r="AA18" s="16" t="n"/>
+      <c r="AD18" s="22" t="n"/>
+      <c r="AE18" s="15" t="n"/>
+      <c r="AF18" s="15" t="n"/>
+      <c r="AG18" s="16" t="n"/>
+      <c r="AH18" s="48" t="n"/>
+      <c r="AI18" s="48" t="n"/>
+      <c r="AJ18" s="23" t="n"/>
+      <c r="AK18" s="15" t="n"/>
+      <c r="AL18" s="15" t="n"/>
+      <c r="AM18" s="16" t="n"/>
+      <c r="AP18" s="23" t="n"/>
+      <c r="AQ18" s="15" t="n"/>
+      <c r="AR18" s="15" t="n"/>
+      <c r="AS18" s="16" t="n"/>
+    </row>
+    <row r="19" s="71">
+      <c r="D19" s="18" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="R19" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="S19" s="15" t="n"/>
+      <c r="T19" s="15" t="n"/>
+      <c r="U19" s="16" t="n"/>
+      <c r="X19" s="21" t="n"/>
+      <c r="Y19" s="15" t="n"/>
+      <c r="Z19" s="15" t="n"/>
+      <c r="AA19" s="16" t="n"/>
+      <c r="AD19" s="22" t="n"/>
+      <c r="AE19" s="15" t="n"/>
+      <c r="AF19" s="15" t="n"/>
+      <c r="AG19" s="16" t="n"/>
+      <c r="AH19" s="48" t="n"/>
+      <c r="AI19" s="48" t="n"/>
+      <c r="AJ19" s="23" t="n"/>
+      <c r="AK19" s="15" t="n"/>
+      <c r="AL19" s="15" t="n"/>
+      <c r="AM19" s="16" t="n"/>
+      <c r="AP19" s="23" t="n"/>
+      <c r="AQ19" s="15" t="n"/>
+      <c r="AR19" s="15" t="n"/>
+      <c r="AS19" s="16" t="n"/>
+    </row>
+    <row r="20" ht="6.75" customHeight="1" s="71">
+      <c r="A20" s="27" t="n"/>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="35" t="n"/>
+      <c r="I20" s="35" t="n"/>
+      <c r="J20" s="36" t="n"/>
+      <c r="K20" s="36" t="n"/>
+      <c r="L20" s="36" t="n"/>
+      <c r="M20" s="35" t="n"/>
+      <c r="N20" s="30" t="n"/>
+      <c r="O20" s="30" t="n"/>
+      <c r="P20" s="30" t="n"/>
+      <c r="Q20" s="30" t="n"/>
+      <c r="R20" s="35" t="n"/>
+      <c r="S20" s="35" t="n"/>
+      <c r="T20" s="35" t="n"/>
+      <c r="U20" s="35" t="n"/>
+      <c r="V20" s="35" t="n"/>
+      <c r="W20" s="35" t="n"/>
+      <c r="X20" s="31" t="n"/>
+      <c r="Y20" s="35" t="n"/>
+      <c r="Z20" s="35" t="n"/>
+      <c r="AA20" s="36" t="n"/>
+      <c r="AB20" s="35" t="n"/>
+      <c r="AC20" s="35" t="n"/>
+      <c r="AD20" s="32" t="n"/>
+      <c r="AE20" s="35" t="n"/>
+      <c r="AF20" s="35" t="n"/>
+      <c r="AG20" s="36" t="n"/>
+      <c r="AH20" s="35" t="n"/>
+      <c r="AI20" s="35" t="n"/>
+      <c r="AJ20" s="34" t="n"/>
+      <c r="AK20" s="35" t="n"/>
+      <c r="AL20" s="35" t="n"/>
+      <c r="AM20" s="36" t="n"/>
+      <c r="AN20" s="35" t="n"/>
+      <c r="AO20" s="35" t="n"/>
+      <c r="AP20" s="34" t="n"/>
+      <c r="AQ20" s="35" t="n"/>
+      <c r="AR20" s="35" t="n"/>
+      <c r="AS20" s="36" t="n"/>
+      <c r="AT20" s="35" t="n"/>
+      <c r="AU20" s="35" t="n"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" s="71">
+      <c r="A21" s="10">
+        <f>IMAGE("https://ae-pic-a1.aliexpress-media.com/kf/S285a95bb17834cdc964b778e4ab9a080L.jpg")</f>
+        <v/>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Deer Hanger Pulley Lift System Rated 700 Lbs Gambrel for Skinning with…</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>AliExpress: US $16.89. Vår räkning: landad ca 242 kr, tänkt butikspris 599 kr. Originaltitel: Deer Hanger Pulley Lift System Rated 700 Lbs Gambrel for Skinning with Wear-Resistant Tangle-Free Rope Deer Hunting Accessories</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>SWEDEN</t>
+        </is>
+      </c>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="15" t="n"/>
+      <c r="L21" s="16" t="n"/>
+      <c r="M21" s="14" t="n"/>
+      <c r="N21" s="17" t="inlineStr">
+        <is>
+          <t>https://www.aliexpress.com/item/1005012116406743.html</t>
+        </is>
+      </c>
+      <c r="Q21" s="18" t="n"/>
+      <c r="R21" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="S21" s="15" t="n"/>
+      <c r="T21" s="15" t="n"/>
+      <c r="U21" s="16" t="n"/>
+      <c r="V21" s="48" t="n"/>
+      <c r="W21" s="48" t="n"/>
+      <c r="X21" s="21" t="n"/>
+      <c r="Y21" s="15" t="n"/>
+      <c r="Z21" s="15" t="n"/>
+      <c r="AA21" s="16" t="n"/>
+      <c r="AB21" s="48" t="n"/>
+      <c r="AC21" s="48" t="n"/>
+      <c r="AD21" s="22" t="n"/>
+      <c r="AE21" s="15" t="n"/>
+      <c r="AF21" s="15" t="n"/>
+      <c r="AG21" s="16" t="n"/>
+      <c r="AH21" s="48" t="n"/>
+      <c r="AI21" s="48" t="n"/>
+      <c r="AJ21" s="23" t="n"/>
+      <c r="AK21" s="15" t="n"/>
+      <c r="AL21" s="15" t="n"/>
+      <c r="AM21" s="16" t="n"/>
+      <c r="AN21" s="25" t="n"/>
+      <c r="AO21" s="48" t="n"/>
+      <c r="AP21" s="23" t="n"/>
+      <c r="AQ21" s="15" t="n"/>
+      <c r="AR21" s="15" t="n"/>
+      <c r="AS21" s="16" t="n"/>
+      <c r="AT21" s="25" t="n"/>
+      <c r="AU21" s="26" t="n"/>
+    </row>
+    <row r="22" ht="25.5" customHeight="1" s="71">
+      <c r="D22" s="18" t="n"/>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="16" t="n"/>
+      <c r="R22" s="19" t="n">
+        <v>200</v>
+      </c>
+      <c r="S22" s="15" t="n"/>
+      <c r="T22" s="15" t="n"/>
+      <c r="U22" s="16" t="n"/>
+      <c r="X22" s="21" t="n"/>
+      <c r="Y22" s="15" t="n"/>
+      <c r="Z22" s="15" t="n"/>
+      <c r="AA22" s="16" t="n"/>
+      <c r="AD22" s="22" t="n"/>
+      <c r="AE22" s="15" t="n"/>
+      <c r="AF22" s="15" t="n"/>
+      <c r="AG22" s="16" t="n"/>
+      <c r="AH22" s="48" t="n"/>
+      <c r="AI22" s="48" t="n"/>
+      <c r="AJ22" s="23" t="n"/>
+      <c r="AK22" s="15" t="n"/>
+      <c r="AL22" s="15" t="n"/>
+      <c r="AM22" s="16" t="n"/>
+      <c r="AP22" s="23" t="n"/>
+      <c r="AQ22" s="15" t="n"/>
+      <c r="AR22" s="15" t="n"/>
+      <c r="AS22" s="16" t="n"/>
+    </row>
+    <row r="23" s="71">
+      <c r="D23" s="18" t="n"/>
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="15" t="n"/>
+      <c r="L23" s="16" t="n"/>
+      <c r="R23" s="19" t="n">
+        <v>300</v>
+      </c>
+      <c r="S23" s="15" t="n"/>
+      <c r="T23" s="15" t="n"/>
+      <c r="U23" s="16" t="n"/>
+      <c r="X23" s="21" t="n"/>
+      <c r="Y23" s="15" t="n"/>
+      <c r="Z23" s="15" t="n"/>
+      <c r="AA23" s="16" t="n"/>
+      <c r="AD23" s="22" t="n"/>
+      <c r="AE23" s="15" t="n"/>
+      <c r="AF23" s="15" t="n"/>
+      <c r="AG23" s="16" t="n"/>
+      <c r="AH23" s="48" t="n"/>
+      <c r="AI23" s="48" t="n"/>
+      <c r="AJ23" s="23" t="n"/>
+      <c r="AK23" s="15" t="n"/>
+      <c r="AL23" s="15" t="n"/>
+      <c r="AM23" s="16" t="n"/>
+      <c r="AP23" s="23" t="n"/>
+      <c r="AQ23" s="15" t="n"/>
+      <c r="AR23" s="15" t="n"/>
+      <c r="AS23" s="16" t="n"/>
+    </row>
+    <row r="24" ht="6.75" customHeight="1" s="71">
+      <c r="A24" s="27" t="n"/>
+      <c r="B24" s="27" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="27" t="n"/>
+      <c r="H24" s="35" t="n"/>
+      <c r="I24" s="35" t="n"/>
+      <c r="J24" s="36" t="n"/>
+      <c r="K24" s="36" t="n"/>
+      <c r="L24" s="36" t="n"/>
+      <c r="M24" s="35" t="n"/>
+      <c r="N24" s="30" t="n"/>
+      <c r="O24" s="30" t="n"/>
+      <c r="P24" s="30" t="n"/>
+      <c r="Q24" s="30" t="n"/>
+      <c r="R24" s="35" t="n"/>
+      <c r="S24" s="35" t="n"/>
+      <c r="T24" s="35" t="n"/>
+      <c r="U24" s="35" t="n"/>
+      <c r="V24" s="35" t="n"/>
+      <c r="W24" s="35" t="n"/>
+      <c r="X24" s="31" t="n"/>
+      <c r="Y24" s="35" t="n"/>
+      <c r="Z24" s="35" t="n"/>
+      <c r="AA24" s="36" t="n"/>
+      <c r="AB24" s="35" t="n"/>
+      <c r="AC24" s="35" t="n"/>
+      <c r="AD24" s="32" t="n"/>
+      <c r="AE24" s="35" t="n"/>
+      <c r="AF24" s="35" t="n"/>
+      <c r="AG24" s="36" t="n"/>
+      <c r="AH24" s="35" t="n"/>
+      <c r="AI24" s="35" t="n"/>
+      <c r="AJ24" s="34" t="n"/>
+      <c r="AK24" s="35" t="n"/>
+      <c r="AL24" s="35" t="n"/>
+      <c r="AM24" s="36" t="n"/>
+      <c r="AN24" s="35" t="n"/>
+      <c r="AO24" s="35" t="n"/>
+      <c r="AP24" s="34" t="n"/>
+      <c r="AQ24" s="35" t="n"/>
+      <c r="AR24" s="35" t="n"/>
+      <c r="AS24" s="36" t="n"/>
+      <c r="AT24" s="35" t="n"/>
+      <c r="AU24" s="35" t="n"/>
+    </row>
     <row r="25" ht="22.5" customHeight="1" s="71"/>
     <row r="26" ht="22.5" customHeight="1" s="71"/>
     <row r="27" ht="22.5" customHeight="1" s="71"/>
@@ -2360,39 +2867,63 @@
     <row r="999" ht="15.75" customHeight="1" s="71"/>
     <row r="1000" ht="15.75" customHeight="1" s="71"/>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="52">
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="E5:G7"/>
     <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="M21:M23"/>
     <mergeCell ref="L3:L4"/>
+    <mergeCell ref="E13:G15"/>
     <mergeCell ref="X3:AC3"/>
+    <mergeCell ref="N21:P23"/>
     <mergeCell ref="N5:P7"/>
+    <mergeCell ref="H13:H15"/>
     <mergeCell ref="E3:G4"/>
     <mergeCell ref="AJ3:AO3"/>
+    <mergeCell ref="M17:M19"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="Q17:Q19"/>
     <mergeCell ref="E9:G11"/>
     <mergeCell ref="R3:W3"/>
+    <mergeCell ref="A21:C23"/>
     <mergeCell ref="A1:AO1"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="I3:I4"/>
+    <mergeCell ref="Q13:Q15"/>
+    <mergeCell ref="N13:P15"/>
+    <mergeCell ref="N17:P19"/>
+    <mergeCell ref="A17:C19"/>
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I9:I11"/>
     <mergeCell ref="A5:C7"/>
     <mergeCell ref="N3:P4"/>
     <mergeCell ref="M9:M11"/>
     <mergeCell ref="M5:M7"/>
+    <mergeCell ref="A13:C15"/>
+    <mergeCell ref="Q21:Q23"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="N9:P11"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="A3:C4"/>
     <mergeCell ref="AD3:AI3"/>
+    <mergeCell ref="E21:G23"/>
     <mergeCell ref="Q5:Q7"/>
     <mergeCell ref="AP3:AU3"/>
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="A2:AO2"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="A9:C11"/>
+    <mergeCell ref="H21:H23"/>
     <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="E17:G19"/>
+    <mergeCell ref="M13:M15"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
